--- a/data/sars/pacific/tables/Pacific_2012_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2012_Appendix3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F1AFAF-6BD0-0A4A-88ED-CF2F54B7401B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F6C879-BBBB-1F4D-B724-9DFE093C570B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="940" windowWidth="32620" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3220" yWindow="520" windowWidth="32620" windowHeight="20180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="124">
   <si>
     <t>California sea lion</t>
   </si>
@@ -334,9 +334,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>Bryde’s whale</t>
   </si>
   <si>
@@ -383,6 +380,21 @@
   </si>
   <si>
     <t>≥4</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
   </si>
 </sst>
 </file>
@@ -393,7 +405,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -412,13 +424,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -455,7 +460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -517,9 +522,6 @@
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -838,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:R80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.59765625" bestFit="1" customWidth="1"/>
@@ -853,11 +855,11 @@
     <col min="11" max="11" width="14.19921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="43.19921875" customWidth="1"/>
+    <col min="16" max="17" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="43.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>89</v>
       </c>
@@ -880,7 +882,7 @@
         <v>95</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>96</v>
@@ -904,11 +906,16 @@
         <v>102</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+        <v>123</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -937,10 +944,10 @@
         <v>9200</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>4</v>
@@ -957,9 +964,10 @@
       <c r="P2" s="6">
         <v>2011</v>
       </c>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q2" s="6"/>
+      <c r="R2" s="1"/>
+    </row>
+    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -1008,9 +1016,10 @@
       <c r="P3" s="6">
         <v>2011</v>
       </c>
-      <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="1"/>
+    </row>
+    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1039,10 +1048,10 @@
         <v>9</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>4</v>
@@ -1055,9 +1064,10 @@
       <c r="P4" s="6">
         <v>2010</v>
       </c>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q4" s="6"/>
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -1086,10 +1096,10 @@
         <v>9</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>4</v>
@@ -1102,9 +1112,10 @@
       <c r="P5" s="6">
         <v>2010</v>
       </c>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q5" s="6"/>
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -1133,10 +1144,10 @@
         <v>4382</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>4</v>
@@ -1153,9 +1164,10 @@
       <c r="P6" s="6">
         <v>2007</v>
       </c>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q6" s="6"/>
+      <c r="R6" s="1"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1200,9 +1212,10 @@
       <c r="P7" s="6">
         <v>2000</v>
       </c>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q7" s="6"/>
+      <c r="R7" s="1"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1251,9 +1264,10 @@
       <c r="P8" s="6">
         <v>2010</v>
       </c>
-      <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q8" s="6"/>
+      <c r="R8" s="1"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="10" t="s">
         <v>18</v>
       </c>
@@ -1302,9 +1316,12 @@
       <c r="P9" s="14">
         <v>2012</v>
       </c>
-      <c r="Q9" s="1"/>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q9" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R9" s="1"/>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>22</v>
       </c>
@@ -1353,9 +1370,10 @@
       <c r="P10" s="6">
         <v>2009</v>
       </c>
-      <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q10" s="6"/>
+      <c r="R10" s="1"/>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
@@ -1384,10 +1402,10 @@
         <v>10</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>4</v>
@@ -1404,9 +1422,10 @@
       <c r="P11" s="6">
         <v>2009</v>
       </c>
-      <c r="Q11" s="1"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q11" s="6"/>
+      <c r="R11" s="1"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -1455,9 +1474,10 @@
       <c r="P12" s="6">
         <v>2009</v>
       </c>
-      <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q12" s="6"/>
+      <c r="R12" s="1"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -1486,10 +1506,10 @@
         <v>577</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>4</v>
@@ -1506,9 +1526,10 @@
       <c r="P13" s="6">
         <v>2009</v>
       </c>
-      <c r="Q13" s="1"/>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q13" s="6"/>
+      <c r="R13" s="1"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -1557,9 +1578,10 @@
       <c r="P14" s="6">
         <v>2011</v>
       </c>
-      <c r="Q14" s="1"/>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q14" s="6"/>
+      <c r="R14" s="1"/>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -1608,9 +1630,10 @@
       <c r="P15" s="6">
         <v>2011</v>
       </c>
-      <c r="Q15" s="1"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q15" s="6"/>
+      <c r="R15" s="1"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1639,10 +1662,10 @@
         <v>257</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>4</v>
@@ -1659,9 +1682,10 @@
       <c r="P16" s="6">
         <v>2010</v>
       </c>
-      <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q16" s="6"/>
+      <c r="R16" s="1"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
@@ -1710,9 +1734,10 @@
       <c r="P17" s="6">
         <v>2010</v>
       </c>
-      <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q17" s="6"/>
+      <c r="R17" s="1"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -1761,9 +1786,10 @@
       <c r="P18" s="6">
         <v>2010</v>
       </c>
-      <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q18" s="6"/>
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
@@ -1812,9 +1838,10 @@
       <c r="P19" s="6">
         <v>2008</v>
       </c>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q19" s="6"/>
+      <c r="R19" s="1"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
@@ -1843,10 +1870,10 @@
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>4</v>
@@ -1863,9 +1890,10 @@
       <c r="P20" s="6">
         <v>2010</v>
       </c>
-      <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q20" s="6"/>
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -1914,9 +1942,10 @@
       <c r="P21" s="6">
         <v>2010</v>
       </c>
-      <c r="Q21" s="1"/>
-    </row>
-    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q21" s="6"/>
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
@@ -1965,9 +1994,10 @@
       <c r="P22" s="6">
         <v>2010</v>
       </c>
-      <c r="Q22" s="1"/>
-    </row>
-    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q22" s="6"/>
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="15" t="s">
         <v>40</v>
       </c>
@@ -2016,9 +2046,12 @@
       <c r="P23" s="19">
         <v>2012</v>
       </c>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q23" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>41</v>
       </c>
@@ -2067,14 +2100,15 @@
       <c r="P24" s="6">
         <v>2010</v>
       </c>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" spans="1:17" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q24" s="6"/>
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>2</v>
@@ -2119,13 +2153,14 @@
         <v>2010</v>
       </c>
       <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="1:17" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10" t="s">
         <v>78</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>88</v>
@@ -2169,9 +2204,12 @@
       <c r="P26" s="10">
         <v>2012</v>
       </c>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q26" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>42</v>
       </c>
@@ -2194,7 +2232,7 @@
         <v>0.04</v>
       </c>
       <c r="H27" s="9">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="9">
         <v>4.5999999999999996</v>
@@ -2220,9 +2258,12 @@
       <c r="P27" s="6">
         <v>2010</v>
       </c>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q27" s="6"/>
+      <c r="R27" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
         <v>43</v>
       </c>
@@ -2271,9 +2312,10 @@
       <c r="P28" s="6">
         <v>2010</v>
       </c>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q28" s="6"/>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -2322,9 +2364,10 @@
       <c r="P29" s="6">
         <v>2010</v>
       </c>
-      <c r="Q29" s="1"/>
-    </row>
-    <row r="30" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q29" s="6"/>
+      <c r="R29" s="1"/>
+    </row>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
         <v>45</v>
       </c>
@@ -2373,9 +2416,10 @@
       <c r="P30" s="6">
         <v>2010</v>
       </c>
-      <c r="Q30" s="1"/>
-    </row>
-    <row r="31" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q30" s="6"/>
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>46</v>
       </c>
@@ -2424,9 +2468,10 @@
       <c r="P31" s="6">
         <v>2010</v>
       </c>
-      <c r="Q31" s="1"/>
-    </row>
-    <row r="32" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q31" s="6"/>
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
         <v>47</v>
       </c>
@@ -2475,9 +2520,10 @@
       <c r="P32" s="6">
         <v>2010</v>
       </c>
-      <c r="Q32" s="1"/>
-    </row>
-    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q32" s="6"/>
+      <c r="R32" s="1"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="15" t="s">
         <v>48</v>
       </c>
@@ -2526,9 +2572,12 @@
       <c r="P33" s="19">
         <v>2012</v>
       </c>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q33" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="15" t="s">
         <v>49</v>
       </c>
@@ -2574,12 +2623,15 @@
       <c r="O34" s="19">
         <v>2011</v>
       </c>
-      <c r="P34" s="21">
+      <c r="P34" s="19">
         <v>2011</v>
       </c>
-      <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q34" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>51</v>
       </c>
@@ -2628,9 +2680,10 @@
       <c r="P35" s="6">
         <v>2010</v>
       </c>
-      <c r="Q35" s="1"/>
-    </row>
-    <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q35" s="6"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
         <v>54</v>
       </c>
@@ -2679,9 +2732,10 @@
       <c r="P36" s="6">
         <v>2010</v>
       </c>
-      <c r="Q36" s="1"/>
-    </row>
-    <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q36" s="6"/>
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
         <v>55</v>
       </c>
@@ -2730,9 +2784,10 @@
       <c r="P37" s="6">
         <v>2010</v>
       </c>
-      <c r="Q37" s="1"/>
-    </row>
-    <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q37" s="6"/>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>56</v>
       </c>
@@ -2781,9 +2836,10 @@
       <c r="P38" s="6">
         <v>2010</v>
       </c>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="39" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q38" s="6"/>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>57</v>
       </c>
@@ -2832,9 +2888,10 @@
       <c r="P39" s="6">
         <v>2010</v>
       </c>
-      <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q39" s="6"/>
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
         <v>58</v>
       </c>
@@ -2879,9 +2936,10 @@
       <c r="P40" s="6">
         <v>2010</v>
       </c>
-      <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q40" s="6"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>58</v>
       </c>
@@ -2930,9 +2988,10 @@
       <c r="P41" s="6">
         <v>2010</v>
       </c>
-      <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q41" s="6"/>
+      <c r="R41" s="1"/>
+    </row>
+    <row r="42" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
         <v>34</v>
       </c>
@@ -2977,9 +3036,10 @@
       <c r="P42" s="6">
         <v>2010</v>
       </c>
-      <c r="Q42" s="1"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q42" s="6"/>
+      <c r="R42" s="1"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>35</v>
       </c>
@@ -3008,10 +3068,10 @@
         <v>18</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
@@ -3024,9 +3084,10 @@
       <c r="P43" s="6">
         <v>2010</v>
       </c>
-      <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q43" s="6"/>
+      <c r="R43" s="1"/>
+    </row>
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
         <v>35</v>
       </c>
@@ -3075,9 +3136,10 @@
       <c r="P44" s="6">
         <v>2010</v>
       </c>
-      <c r="Q44" s="1"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q44" s="6"/>
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>35</v>
       </c>
@@ -3126,9 +3188,10 @@
       <c r="P45" s="6">
         <v>2010</v>
       </c>
-      <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q45" s="6"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
         <v>35</v>
       </c>
@@ -3177,9 +3240,10 @@
       <c r="P46" s="6">
         <v>2010</v>
       </c>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q46" s="6"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
         <v>35</v>
       </c>
@@ -3228,9 +3292,10 @@
       <c r="P47" s="6">
         <v>2010</v>
       </c>
-      <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q47" s="6"/>
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
         <v>65</v>
       </c>
@@ -3275,9 +3340,10 @@
       <c r="P48" s="6">
         <v>2010</v>
       </c>
-      <c r="Q48" s="1"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q48" s="6"/>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="15" t="s">
         <v>66</v>
       </c>
@@ -3326,9 +3392,12 @@
       <c r="P49" s="19">
         <v>2012</v>
       </c>
-      <c r="Q49" s="1"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q49" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="15" t="s">
         <v>66</v>
       </c>
@@ -3365,7 +3434,7 @@
       <c r="L50" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="M50" s="22"/>
+      <c r="M50" s="21"/>
       <c r="N50" s="19">
         <v>1994</v>
       </c>
@@ -3375,9 +3444,12 @@
       <c r="P50" s="19">
         <v>2012</v>
       </c>
-      <c r="Q50" s="1"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q50" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="15" t="s">
         <v>66</v>
       </c>
@@ -3426,9 +3498,12 @@
       <c r="P51" s="19">
         <v>2012</v>
       </c>
-      <c r="Q51" s="1"/>
-    </row>
-    <row r="52" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q51" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R51" s="1"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="15" t="s">
         <v>66</v>
       </c>
@@ -3477,9 +3552,12 @@
       <c r="P52" s="19">
         <v>2012</v>
       </c>
-      <c r="Q52" s="1"/>
-    </row>
-    <row r="53" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q52" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="15" t="s">
         <v>66</v>
       </c>
@@ -3516,7 +3594,7 @@
       <c r="L53" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="M53" s="22"/>
+      <c r="M53" s="21"/>
       <c r="N53" s="19">
         <v>1998</v>
       </c>
@@ -3526,9 +3604,12 @@
       <c r="P53" s="19">
         <v>2012</v>
       </c>
-      <c r="Q53" s="1"/>
-    </row>
-    <row r="54" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q53" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="15" t="s">
         <v>66</v>
       </c>
@@ -3577,9 +3658,12 @@
       <c r="P54" s="19">
         <v>2012</v>
       </c>
-      <c r="Q54" s="1"/>
-    </row>
-    <row r="55" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q54" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R54" s="1"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
         <v>66</v>
       </c>
@@ -3628,9 +3712,10 @@
       <c r="P55" s="6">
         <v>2010</v>
       </c>
-      <c r="Q55" s="1"/>
-    </row>
-    <row r="56" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q55" s="6"/>
+      <c r="R55" s="1"/>
+    </row>
+    <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
@@ -3675,9 +3760,10 @@
       <c r="P56" s="6">
         <v>2010</v>
       </c>
-      <c r="Q56" s="1"/>
-    </row>
-    <row r="57" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q56" s="6"/>
+      <c r="R56" s="1"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
         <v>71</v>
       </c>
@@ -3722,9 +3808,10 @@
       <c r="P57" s="6">
         <v>2010</v>
       </c>
-      <c r="Q57" s="1"/>
-    </row>
-    <row r="58" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q57" s="6"/>
+      <c r="R57" s="1"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
         <v>72</v>
       </c>
@@ -3769,9 +3856,10 @@
       <c r="P58" s="6">
         <v>2010</v>
       </c>
-      <c r="Q58" s="1"/>
-    </row>
-    <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q58" s="6"/>
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
         <v>73</v>
       </c>
@@ -3816,9 +3904,10 @@
       <c r="P59" s="6">
         <v>2010</v>
       </c>
-      <c r="Q59" s="1"/>
-    </row>
-    <row r="60" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q59" s="6"/>
+      <c r="R59" s="1"/>
+    </row>
+    <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="15" t="s">
         <v>74</v>
       </c>
@@ -3855,17 +3944,20 @@
       <c r="L60" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
       <c r="O60" s="19">
         <v>2010</v>
       </c>
       <c r="P60" s="19">
         <v>2012</v>
       </c>
-      <c r="Q60" s="1"/>
-    </row>
-    <row r="61" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q60" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R60" s="1"/>
+    </row>
+    <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10" t="s">
         <v>74</v>
       </c>
@@ -3902,7 +3994,7 @@
       <c r="L61" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="M61" s="23"/>
+      <c r="M61" s="22"/>
       <c r="N61" s="14">
         <v>2002</v>
       </c>
@@ -3912,9 +4004,12 @@
       <c r="P61" s="14">
         <v>2012</v>
       </c>
-      <c r="Q61" s="1"/>
-    </row>
-    <row r="62" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q61" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R61" s="1"/>
+    </row>
+    <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10" t="s">
         <v>74</v>
       </c>
@@ -3951,17 +4046,20 @@
       <c r="L62" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="M62" s="23"/>
-      <c r="N62" s="23"/>
+      <c r="M62" s="22"/>
+      <c r="N62" s="22"/>
       <c r="O62" s="14">
         <v>2005</v>
       </c>
       <c r="P62" s="14">
         <v>2012</v>
       </c>
-      <c r="Q62" s="1"/>
-    </row>
-    <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q62" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R62" s="1"/>
+    </row>
+    <row r="63" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10" t="s">
         <v>74</v>
       </c>
@@ -4010,9 +4108,12 @@
       <c r="P63" s="14">
         <v>2012</v>
       </c>
-      <c r="Q63" s="1"/>
-    </row>
-    <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q63" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="R63" s="1"/>
+    </row>
+    <row r="64" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
         <v>74</v>
       </c>
@@ -4061,9 +4162,10 @@
       <c r="P64" s="6">
         <v>2010</v>
       </c>
-      <c r="Q64" s="1"/>
-    </row>
-    <row r="65" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q64" s="6"/>
+      <c r="R64" s="1"/>
+    </row>
+    <row r="65" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
         <v>78</v>
       </c>
@@ -4108,9 +4210,10 @@
       <c r="P65" s="6">
         <v>2010</v>
       </c>
-      <c r="Q65" s="1"/>
-    </row>
-    <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q65" s="6"/>
+      <c r="R65" s="1"/>
+    </row>
+    <row r="66" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
         <v>79</v>
       </c>
@@ -4155,9 +4258,10 @@
       <c r="P66" s="6">
         <v>2010</v>
       </c>
-      <c r="Q66" s="1"/>
-    </row>
-    <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q66" s="6"/>
+      <c r="R66" s="1"/>
+    </row>
+    <row r="67" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
         <v>80</v>
       </c>
@@ -4202,9 +4306,10 @@
       <c r="P67" s="6">
         <v>2010</v>
       </c>
-      <c r="Q67" s="1"/>
-    </row>
-    <row r="68" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q67" s="6"/>
+      <c r="R67" s="1"/>
+    </row>
+    <row r="68" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
         <v>81</v>
       </c>
@@ -4249,9 +4354,10 @@
       <c r="P68" s="6">
         <v>2010</v>
       </c>
-      <c r="Q68" s="1"/>
-    </row>
-    <row r="69" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q68" s="6"/>
+      <c r="R68" s="1"/>
+    </row>
+    <row r="69" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
@@ -4296,9 +4402,10 @@
       <c r="P69" s="6">
         <v>2010</v>
       </c>
-      <c r="Q69" s="1"/>
-    </row>
-    <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q69" s="6"/>
+      <c r="R69" s="1"/>
+    </row>
+    <row r="70" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
         <v>82</v>
       </c>
@@ -4343,9 +4450,10 @@
       <c r="P70" s="6">
         <v>2010</v>
       </c>
-      <c r="Q70" s="1"/>
-    </row>
-    <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q70" s="6"/>
+      <c r="R70" s="1"/>
+    </row>
+    <row r="71" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
         <v>47</v>
       </c>
@@ -4390,9 +4498,10 @@
       <c r="P71" s="6">
         <v>2010</v>
       </c>
-      <c r="Q71" s="1"/>
-    </row>
-    <row r="72" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q71" s="6"/>
+      <c r="R71" s="1"/>
+    </row>
+    <row r="72" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
         <v>48</v>
       </c>
@@ -4437,9 +4546,10 @@
       <c r="P72" s="6">
         <v>2010</v>
       </c>
-      <c r="Q72" s="1"/>
-    </row>
-    <row r="73" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q72" s="6"/>
+      <c r="R72" s="1"/>
+    </row>
+    <row r="73" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
         <v>54</v>
       </c>
@@ -4484,9 +4594,10 @@
       <c r="P73" s="6">
         <v>2010</v>
       </c>
-      <c r="Q73" s="1"/>
-    </row>
-    <row r="74" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q73" s="6"/>
+      <c r="R73" s="1"/>
+    </row>
+    <row r="74" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
         <v>55</v>
       </c>
@@ -4531,11 +4642,12 @@
       <c r="P74" s="6">
         <v>2010</v>
       </c>
-      <c r="Q74" s="1"/>
-    </row>
-    <row r="75" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q74" s="6"/>
+      <c r="R74" s="1"/>
+    </row>
+    <row r="75" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>19</v>
@@ -4543,44 +4655,45 @@
       <c r="C75" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="23">
         <v>469</v>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="23">
         <v>0.45</v>
       </c>
-      <c r="F75" s="24">
+      <c r="F75" s="23">
         <v>327</v>
       </c>
-      <c r="G75" s="24">
-        <v>0.04</v>
-      </c>
-      <c r="H75" s="24">
+      <c r="G75" s="23">
+        <v>0.04</v>
+      </c>
+      <c r="H75" s="23">
         <v>0.5</v>
       </c>
-      <c r="I75" s="24">
+      <c r="I75" s="23">
         <v>3.3</v>
       </c>
-      <c r="J75" s="24">
-        <v>0</v>
-      </c>
-      <c r="K75" s="24">
+      <c r="J75" s="23">
+        <v>0</v>
+      </c>
+      <c r="K75" s="23">
         <v>0</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M75" s="25"/>
-      <c r="N75" s="25"/>
+      <c r="M75" s="24"/>
+      <c r="N75" s="24"/>
       <c r="O75" s="6">
         <v>2002</v>
       </c>
       <c r="P75" s="6">
         <v>2010</v>
       </c>
-      <c r="Q75" s="2"/>
-    </row>
-    <row r="76" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q75" s="6"/>
+      <c r="R75" s="2"/>
+    </row>
+    <row r="76" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
         <v>56</v>
       </c>
@@ -4590,44 +4703,45 @@
       <c r="C76" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="24">
+      <c r="D76" s="23">
         <v>77</v>
       </c>
-      <c r="E76" s="24">
+      <c r="E76" s="23">
         <v>1.06</v>
       </c>
-      <c r="F76" s="24">
+      <c r="F76" s="23">
         <v>37</v>
       </c>
       <c r="G76" s="3">
         <v>0.04</v>
       </c>
-      <c r="H76" s="24">
+      <c r="H76" s="23">
         <v>0.1</v>
       </c>
-      <c r="I76" s="24">
+      <c r="I76" s="23">
         <v>0.1</v>
       </c>
-      <c r="J76" s="24">
-        <v>0</v>
-      </c>
-      <c r="K76" s="24">
+      <c r="J76" s="23">
+        <v>0</v>
+      </c>
+      <c r="K76" s="23">
         <v>0</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M76" s="25"/>
-      <c r="N76" s="25"/>
+      <c r="M76" s="24"/>
+      <c r="N76" s="24"/>
       <c r="O76" s="6">
         <v>2002</v>
       </c>
       <c r="P76" s="6">
         <v>2010</v>
       </c>
-      <c r="Q76" s="2"/>
-    </row>
-    <row r="77" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q76" s="6"/>
+      <c r="R76" s="2"/>
+    </row>
+    <row r="77" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
         <v>57</v>
       </c>
@@ -4672,9 +4786,10 @@
       <c r="P77" s="6">
         <v>2010</v>
       </c>
-      <c r="Q77" s="1"/>
-    </row>
-    <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q77" s="6"/>
+      <c r="R77" s="1"/>
+    </row>
+    <row r="78" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
         <v>51</v>
       </c>
@@ -4723,9 +4838,10 @@
       <c r="P78" s="6">
         <v>2009</v>
       </c>
-      <c r="Q78" s="2"/>
-    </row>
-    <row r="79" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q78" s="6"/>
+      <c r="R78" s="2"/>
+    </row>
+    <row r="79" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
         <v>84</v>
       </c>
@@ -4754,10 +4870,10 @@
         <v>8</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>15</v>
@@ -4774,9 +4890,10 @@
       <c r="P79" s="6">
         <v>2008</v>
       </c>
-      <c r="Q79" s="1"/>
-    </row>
-    <row r="80" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q79" s="6"/>
+      <c r="R79" s="1"/>
+    </row>
+    <row r="80" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
         <v>84</v>
       </c>
@@ -4805,10 +4922,10 @@
         <v>11</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>4</v>
@@ -4825,10 +4942,10 @@
       <c r="P80" s="6">
         <v>2008</v>
       </c>
-      <c r="Q80" s="1"/>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P80" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>